--- a/data/english_expressions_db.xlsx
+++ b/data/english_expressions_db.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5163,6 +5163,2920 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>ENG-20260527-101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>bests</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>/bests/</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>~를 이기다/능가하다</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Paxton bests Cornyn in Texas Republican Senate primary after Trump endorsement</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Our latest Q3 sales performance bests our competitors' results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ENG-20260527-102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>endorse over</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>/ɪnˈdɔːrs ˈoʊvər/</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>~보다 ~를 지지하다/선호하다</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>President Donald Trump last week endorsed Texas Attorney General Ken Paxton over incumbent Sen. John Cornyn.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>The CEO endorsed the marketing lead over the sales manager for the executive promotion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>ENG-20260527-103</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>incumbent</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>/ɪnˈkʌmbənt/</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>현직의, 재임 중인</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>President Donald Trump last week endorsed Texas Attorney General Ken Paxton over incumbent Sen. John Cornyn.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>The incumbent president is seeking re-election in the upcoming November voting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>ENG-20260527-104</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>reignite</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>/ˌriːɪɡˈnaɪt/</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>다시 불붙다/재점화되다</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>SpaceX-Tesla merger chatter reignites as Musk pushes rocket company towards Nasdaq</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>The launch of the new product reignited consumer interest in the brand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>ENG-20260527-105</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>close to</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>/kloʊs tuː/</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>~와 가까운 관계인, ~와 밀접한</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>With SpaceX headed for the public markets next month, industry experts and people close to Elon Musk are speculating about a potential tie-up with Tesla.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Sources close to the CEO revealed that a restructuring plan is underway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>ENG-20260527-106</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>tie-up</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>/ˈtaɪ ʌp/</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>비즈니스 제휴/합병</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>With SpaceX headed for the public markets next month, industry experts and people close to Elon Musk are speculating about a potential tie-up with Tesla.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>The strategic tie-up between the automobile and battery manufacturers will boost EV production.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ENG-20260527-107</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>top in</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>/tɑːp ɪn/</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>~에서 최고를 기록하다, 상위에 오르다</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>South Korea's SK Hynix and U.S. chip firm Micron become the latest companies to top $1 trillion in market capitalization as the AI rally resumes.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>The pharmaceutical giant managed to top in global sales last fiscal year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ENG-20260527-108</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>rally resumes</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>/ˈræli rɪˈzuːmz/</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>상승세(랠리)가 재개되다</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>South Korea's SK Hynix and U.S. chip firm Micron become the latest companies to top $1 trillion in market capitalization as the AI rally resumes.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>As soon as inflation figures cooled down, the stock market rally resumed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ENG-20260527-109</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>head for mixed open</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>/hed fɔːr mɪkst ˈoʊpən/</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>혼조세 출발을 보이다/향하다</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>European markets head for mixed open as oil prices hold below $100</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Wall Street is heading for a mixed open today as investors await the latest job reports.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ENG-20260527-110</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>assess operations</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>/əˈses ˌɑːpəˈreɪʃənz/</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>운영/작전을 평가하다</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>European stocks are expected to open in mixed territory on Wednesday as regional investors assess the latest military operations against Iran.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>The executive board will assess our overseas operations to cut unnecessary costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ENG-20260527-111</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>reduce reliance</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>/rɪˈduːs rɪˈlaɪəns/</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>의존도를 줄이다</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Low manufacturing costs in China are keeping many European businesses' supply chains in the country despite pressure in the EU to reduce overseas reliance.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Transitioning to cloud services will help us reduce reliance on on-premise hardware.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>ENG-20260527-112</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>immigration rules</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>/ˌmɪˈɡreɪʃən ruːlz/</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>이민 규정/법</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>International graduates say a weak hiring market and changing immigration rules make it harder for them to achieve their American dream of working in the U.S.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>The HR team must stay updated on changing immigration rules for foreign workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>ENG-20260527-113</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>achieve dream</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>/əˈtʃiːv driːm/</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>꿈을 이루다</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>International graduates say a weak hiring market and changing immigration rules make it harder for them to achieve their American dream of working in the U.S.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Hard work and dedication are essential to achieve your professional dreams.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>ENG-20260527-114</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>abrupt removal</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>/əˈbrʌpt rɪˈmuːvəl/</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>갑작스러운 해임/퇴출</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>'Bullying' and 'overbearing' behaviour behind abrupt BP chairman removal</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>The abrupt removal of the CEO left the company's shareholders in shock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>ENG-20260527-115</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>unveil first</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>/ʌnˈveɪl fɜːrst/</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>~를 최초 공개하다/베일을 벗기다</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Ferrari shares slump after it unveils first fully electric car</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>The brand is planning to unveil its first foldable smartphone next month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>ENG-20260527-116</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>family farm</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>/ˈfæməli fɑːrm/</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>가족 경영 농가</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Farmers worry more family farms will be sold unless dairy prices rise quickly.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Many traditional family farms are struggling to compete with corporate agricultural giants.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>ENG-20260527-117</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>national inquiry</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>/ˈnæʃnəl ɪnˈkwaɪəri/</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>국가적 조사</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>The commander leading the national police inquiry says the size of the investigation team would need to double in order to meet its current timeline</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>The government launched a national inquiry to find the root cause of the power grid failure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>ENG-20260527-118</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>lead the inquiry</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>/liːd ðə ɪnˈkwaɪəri/</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>조사를 이끌다/주도하다</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>The commander leading the national police inquiry says the size of the investigation team would need to double in order to meet its current timeline</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>A highly respected retired judge was appointed to lead the inquiry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>ENG-20260527-119</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>size of the team</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>/saɪz ʌv ðə tiːm/</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>팀의 규모</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>The commander leading the national police inquiry says the size of the investigation team would need to double in order to meet its current timeline</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>To accelerate project development, we expanded the size of the software engineering team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ENG-20260527-120</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>meet timeline</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>/miːt ˈtaɪmlaɪn/</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>기한/일정을 맞추다</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>The commander leading the national police inquiry says the size of the investigation team would need to double in order to meet its current timeline</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Everyone worked overtime this week to ensure we could meet the client's timeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ENG-20260527-121</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>train delays</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>/treɪn dɪˈleɪz/</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>기차 연착/지연</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Campaigners welcome the move but say passengers are mostly worried about train fares and delays.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Frequent train delays have caused frustration among daily commuters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>ENG-20260527-122</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>number of applicants</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>/ˈnʌmbər ʌv ˈæplɪkənts/</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>지원자 수</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Lord Wolfson tells the BBC Next now typically receives double the number of applicants for one role than it did two years ago.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>The number of applicants for our internship program doubled compared to last year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>ENG-20260527-123</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>spit out</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>/spɪt aʊt/</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>뱉어내다</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Phoebe spits out her hair.)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>He had to spit out the coffee because it tasted extremely burnt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ENG-20260527-124</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>endearing</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>/ɪnˈdɪərɪŋ/</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>사랑스러운, 정감 있는</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Oh, now, don't listen to him, Pheebs, I think it's endearing.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>His clumsy yet sincere way of presenting was actually quite endearing to the clients.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>ENG-20260527-125</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>there's nothing wrong with</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>/ðerz ˈnʌθɪŋ rɔːŋ wɪð/</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>~하는 것은 아무런 문제가 없다</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>You know, there's nothing wrong with speaking correctly.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>There's nothing wrong with double-checking your report before submission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>ENG-20260527-126</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>get back to work</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>/ɡet bæk tuː wɜːrk/</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>다시 일하러 가다, 본업으로 복귀하다</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Indeed there isn't... I should really get back to work.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>The lunch break is over, so let's get back to work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>ENG-20260527-127</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>the gloves come on</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>/ðə ɡlʌvz kʌm ɑːn/</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>(대조적으로 싸우기 위해) 본색을 드러내다, 본격적으로 싸우다</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>The hair comes out, and the gloves come on.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>The debate started politely, but once market share was discussed, the gloves came on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ENG-20260527-128</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>degenerate into</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>/dɪˈdʒenəreɪt ˈɪntuː/</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>(나쁜 상태로) 퇴보하다/악화되다</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(They degenerate into bickering and Chandler happily starts to smoke, undisturbed.)</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>What started as a constructive meeting quickly degenerated into a shouting match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>ENG-20260527-129</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>go out with</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>/ɡoʊ aʊt wɪð/</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>~와 데이트하다/사귀다</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Did you ever go out with a guy your friends all really like?</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>She has been going out with her coworker for over a year now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ENG-20260527-130</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>feel the thing</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>/fiːl ðə θɪŋ/</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>(연애 감정 등) 강력한 감정적 이끌림을 느끼다</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>I mean, they feel the thing, I don't feel the thing.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>He is incredibly kind, but I just don't feel the thing when we're together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>ENG-20260527-131</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>dump someone</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>/dʌmp ˈsʌmwʌn/</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>~를 차버리다, 관계를 끝내다</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Listen, if that's how you feel about the guy, Monica, dump him!</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>After discovering he had lied, she decided to dump him on the spot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ENG-20260527-132</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>get over it</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>/ɡet ˈoʊvər ɪt/</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>(실연, 역경 등을) 극복하다/잊어버리다</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Well, he's a big boy, he'll get over it.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>It was a major business loss, but we have to get over it and move forward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>ENG-20260527-133</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>have had it with</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>/hæv hæd ɪt wɪð/</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>~에 진저리가 나다, 더는 참을 수 없다</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Hey, y'know, I have had it with you guys and your cancer and your emphysema and your heart disease.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>I have had it with this slow software; we need to upgrade to a better one immediately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ENG-20260527-134</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>the bottom line is</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>/ðə ˈbɑːtəm laɪn ɪz/</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>가장 중요한 요점은/결론은</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>The bottom line is, smoking is cool, and you know it.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>The bottom line is that we must cut costs by 15% to survive this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>ENG-20260527-135</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>what's up</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>/wʌts ʌp/</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>무슨 일이야?, 잘 지내?</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Hey, buddy, what's up!</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Hey Steve, what's up? Are you free for a quick call?</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ENG-20260527-136</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>now and then</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>/naʊ ænd ðen/</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>때때로, 이따금씩</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Well, yeah, I have one now and then.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>We still go out for team dinners now and then to celebrate achievements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ENG-20260527-137</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>put it like that</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>/pʊt ɪt laɪk ðæt/</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>그런 식으로 말을 하다/표현하다</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Gee, y'know, no-one- no-one's ever put it like that before.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>When you put it like that, investing in foreign stock seems much less risky.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>ENG-20260527-138</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>stub out</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>/stʌb aʊt/</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>(담배를) 비벼 끄다</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(He hands the phone back and stubs out his cigarette.)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>He stubbed out his cigar in the ashtray before heading inside.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>ENG-20260527-139</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>nicotine patch</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>/ˈnɪkətiːn pætʃ/</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>니코틴 패치</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Okay. I think it's time to change somebody's nicotine patch. (Does so.)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>He started wearing a nicotine patch to help him quit smoking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ENG-20260527-140</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>alive with pleasure</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>/əˈlaɪv wɪð ˈpleʒər/</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>기쁨/즐거움으로 가득 차 활기가 넘치는</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(deadpan) Ooh, I'm alive with pleasure now.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>The children were alive with pleasure when they arrived at the amusement park.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>ENG-20260527-141</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>You're kidding</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>/jʊr ˈkɪdɪŋ/</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>농담하는 거지?, 설마!</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>You're kidding. Oh my God.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>You're kidding! Did we really secure the contract with Samsung?</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>ENG-20260527-142</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>step in</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>/step ɪn/</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>(의도치 않게 무엇을) 밟다, 개입하다</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>And on my way over here, I stepped in gum. ...What is up with the universe?!</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Watch out! Don't step in that puddle of mud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>ENG-20260527-143</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>What is up with</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>/wʌt ɪz ʌp wɪð/</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>~에 도대체 무슨 문제가 있는 거야?, 왜 저래?</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>And on my way over here, I stepped in gum. ...What is up with the universe?!</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>What is up with our database server? It's incredibly slow today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>ENG-20260527-144</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>get out of</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>/ɡet aʊt ʌv/</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>~에서 나오다</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(dragged in by Monica, he has just gotten out of the shower)</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Let's get out of the conference room so they can start the next meeting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>ENG-20260527-145</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>get a deja vu</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>/ɡet ə ˌdeɪʒɑː ˈvuː/</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>기시감(데자뷰)을 느끼다</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Wait, wait, I'm getting a deja vu ...no, I'm not.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>I'm getting a deja vu; I feel like we discussed this exact topic last month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>ENG-20260527-146</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>break up with</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>/breɪk ʌp wɪð/</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>~와 헤어지다/결별하다</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>I've decided to break up with Alan.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Tom was heartbroken when his girlfriend decided to break up with him.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>ENG-20260527-147</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>let your guard down</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>/let jʊr ɡɑːrd daʊn/</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>경계를 풀다, 마음을 놓다</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>You know.. you let your guard down, you start to really care about someone, and I just- I-</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>In business negotiations, you should never let your guard down completely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>ENG-20260527-148</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>care about</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>/ker əˈbaʊt/</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>~를 아끼다, 신경 쓰다</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>You know.. you let your guard down, you start to really care about someone, and I just- I-</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Our developers genuinely care about user experience and data privacy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>ENG-20260527-149</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>go on pretending</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>/ɡoʊ ɑːn prɪˈtendɪŋ/</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>계속 ~인 체하다, 거짓인 양 행동하다</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Look, I- I could go on pretending-</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>We can't go on pretending that our sales performance is fine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>ENG-20260527-150</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>be fair to</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>/biː fer tuː/</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>~에게 공평하다/정당하다</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>-but that wouldn't be fair to me, it wouldn't be fair to Alan- It wouldn't be fair to you!</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>To be fair to the applicants, we should blind-review all resumes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>ENG-20260527-151</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>want things back</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>/wɑːnt θɪŋz bæk/</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>일들이 이전으로 되돌아가길 원하다</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Who-who wants fair? Y'know, I just want things back. Y'know, the way they were.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>After the stressful corporate restructuring, many employees wanted things back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>ENG-20260527-152</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>with the holidays coming up</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>/wɪð ðə ˈhɑːlɪdeɪz ˈkʌmɪŋ ʌp/</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>연휴/휴일이 코앞에 다가온 시점에</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>I just can't believe this! I mean, with the holidays coming up- I wanted him to meet my family-</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>With the holidays coming up, we expect retail traffic to double.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>ENG-20260527-153</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>overseas reliance</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>/ˌoʊvərˈsiːz rɪˈlaɪəns/</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>해외 의존도</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Low manufacturing costs in China are keeping many European businesses' supply chains in the country despite pressure in the EU to reduce overseas reliance.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>To minimize risk, our long-term strategy is to decrease overseas reliance for microchips.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>ENG-20260527-154</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>weak hiring market</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>/wiːk ˈhaɪərɪŋ ˈmɑːrkɪt/</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>침체된 채용 시장</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>International graduates say a weak hiring market and changing immigration rules make it harder for them to achieve their American dream of working in the U.S.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Job seekers are facing longer interview processes due to a weak hiring market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>ENG-20260527-155</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>BBC_Business</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>have a strong appeal to</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>/hæv ə strɔːŋ əˈpiːl tu/</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>~에게 강력한 매력[호소력]이 있다</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>The advertising watchdog said the adverts featuring top footballers had a strong appeal to under-18s.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>The minimalist interface design of the app has a strong appeal to younger users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>ENG-20260527-156</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>indeed there isn't</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>/ɪnˈdiːd ðɛr ˈɪzənt/</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>정말이지 그렇지요 (상대의 말에 강하게 맞장구치기)</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Rachel: "Indeed there isn't"... I should really get back to work.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>A: There is no excuse for poor customer service. B: Indeed there isn't.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>ENG-20260527-157</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>a cow got through</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>/ə kaʊ ɡɑːt θruː/</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>(예외적으로 아주 드문 실수나 결함이) 뚫고 나오다</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Paula: Waitwait.. we talking about the coyotes here? All right, a cow got through!</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>We have a strict quality control system, but once in a while, a cow gets through.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>ENG-20260527-158</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>big boy</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>idiom</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>/bɪɡ bɔɪ/</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>다 큰 어른, 스스로 감당할 수 있는 성인</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Paula: Well, he's a big boy, he'll get over it.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Don't worry about his reaction to the project's cancellation; he's a big boy and will handle it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>ENG-20260527-159</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>have respect for</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>/hæv rɪˈspɛkt fɔːr/</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>~을 존중하다</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Joey: Do you have any respect for your body?</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>If you want to maintain a good working relationship, you must have respect for your coworkers' time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>ENG-20260527-160</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>hand back</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>/hænd bæk/</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>다시 건네주다, 돌려주다</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>(He hands the phone back and stubs out his cigarette.)</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Please review the document, sign it, and hand it back to the receptionist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>ENG-20260527-161</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>give a dubious look</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>collocation</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>/ɡɪv ə ˈduːbiəs lʊk/</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>의심쩍은 눈빛을 보내다</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(They give each other a dubious look.)</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>The manager gave us a dubious look when we proposed launching the project without testing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>ENG-20260527-162</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>come up</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>/kʌm ʌp/</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>(행사, 고비 등이) 다가오다, 닥치다</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Rachel: (tearful) I just can't believe this! I mean, with the holidays coming up- I wanted him to meet my family-</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>With the annual audit coming up next month, the finance team is working overtime.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
